--- a/app/src/main/assets/Pipistrelli 2025.xlsx
+++ b/app/src/main/assets/Pipistrelli 2025.xlsx
@@ -16,9 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -49,9 +48,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -493,7 +493,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>45659</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -550,10 +550,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>45660</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -610,10 +609,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>45663</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -626,7 +624,6 @@
           <t>Myotis emarginatus</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Bassano del Grappa</t>
@@ -666,10 +663,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>45671</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -682,7 +678,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t xml:space="preserve">Santorso </t>
@@ -722,10 +717,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>45675</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -738,7 +732,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Caltrano</t>
@@ -778,10 +771,9 @@
           <t>in degenza</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>45675</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -838,10 +830,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>45675</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -854,7 +845,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Venezia</t>
@@ -894,10 +884,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>45678</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -910,7 +899,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Modena</t>
@@ -950,10 +938,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>45687</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -966,7 +953,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t xml:space="preserve">Montecchio maggiore </t>
@@ -1006,10 +992,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>45698</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -1022,7 +1007,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Bassano del Grappa</t>
@@ -1057,11 +1041,9 @@
           <t>Trovato nella casa di montagna,in terra,chiuso probabilmente dall'autunno, le guardie forestali di Schio lo hanno fatto mettere in giardino in pieno giorno.</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>45701</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -1074,7 +1056,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Padova</t>
@@ -1114,10 +1095,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>45704</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -1174,10 +1154,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -1190,7 +1169,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Montecchio maggiore</t>
@@ -1230,10 +1208,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>45710</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -1246,7 +1223,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>Arzignano</t>
@@ -1286,10 +1262,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>45710</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -1302,7 +1277,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>Arzignano</t>
@@ -1342,10 +1316,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -1358,7 +1331,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>Longare</t>
@@ -1398,10 +1370,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -1414,7 +1385,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>Piazza Guglielmo Marconi</t>
@@ -1449,11 +1419,9 @@
           <t>Segnalato pipistrello dentro la chiesa</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>45721</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -1510,10 +1478,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>45721</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -1526,7 +1493,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>Padova</t>
@@ -1566,10 +1532,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>45755</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -1626,10 +1591,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>45758</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -1686,10 +1650,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>45768</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -1746,10 +1709,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>45770</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -1762,7 +1724,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>Scandolara</t>
@@ -1802,10 +1763,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>45770</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -1818,7 +1778,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>Lido</t>
@@ -1858,10 +1817,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>45776</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -1874,7 +1832,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>Modica</t>
@@ -1914,10 +1871,9 @@
           <t>in degenza</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -1974,10 +1930,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -2034,10 +1989,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>45780</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -2050,7 +2004,6 @@
           <t>Vespertilio murinus</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>Creazzo</t>
@@ -2090,10 +2043,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>45786</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -2106,7 +2058,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>Terrassa Padovana</t>
@@ -2146,10 +2097,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>45807</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -2162,7 +2112,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>Padova</t>
@@ -2202,10 +2151,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>45810</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -2218,7 +2166,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>Padova</t>
@@ -2258,10 +2205,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>45811</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -2274,7 +2220,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>Dueville</t>
@@ -2314,10 +2259,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>45812</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -2330,7 +2274,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>Creazzo</t>
@@ -2370,10 +2313,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>45812</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -2386,7 +2328,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>Creazzo</t>
@@ -2426,10 +2367,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>45813</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -2442,7 +2382,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>Creazzo</t>
@@ -2482,10 +2421,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>45813</v>
       </c>
       <c r="B37" t="inlineStr">
@@ -2498,7 +2436,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>Via Brigata orobica 9</t>
@@ -2538,10 +2475,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>45813</v>
       </c>
       <c r="B38" t="inlineStr">
@@ -2554,7 +2490,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>Via Andrea Moschetti 7</t>
@@ -2594,10 +2529,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>45813</v>
       </c>
       <c r="B39" t="inlineStr">
@@ -2610,7 +2544,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>Bergamo</t>
@@ -2655,7 +2588,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>45814</v>
       </c>
       <c r="B40" t="inlineStr">
@@ -2668,7 +2601,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>Largo Europa</t>
@@ -2708,10 +2640,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>45815</v>
       </c>
       <c r="B41" t="inlineStr">
@@ -2724,7 +2655,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>Largo Europa</t>
@@ -2764,10 +2694,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>45817</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -2780,7 +2709,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>Piazzola sul Brenta</t>
@@ -2820,10 +2748,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>45819</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -2836,7 +2763,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>Via Corelli</t>
@@ -2876,10 +2802,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>45819</v>
       </c>
       <c r="B44" t="inlineStr">
@@ -2936,10 +2861,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>45819</v>
       </c>
       <c r="B45" t="inlineStr">
@@ -2952,7 +2876,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -2992,10 +2915,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>45819</v>
       </c>
       <c r="B46" t="inlineStr">
@@ -3008,7 +2930,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>Padova</t>
@@ -3053,7 +2974,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>45820</v>
       </c>
       <c r="B47" t="inlineStr">
@@ -3066,7 +2987,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>Via Aulo Gellio Valle 23</t>
@@ -3106,10 +3026,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>45820</v>
       </c>
       <c r="B48" t="inlineStr">
@@ -3122,7 +3041,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>Via Aulo Gellio Valle 23</t>
@@ -3162,10 +3080,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>45820</v>
       </c>
       <c r="B49" t="inlineStr">
@@ -3178,7 +3095,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>Via Baracche</t>
@@ -3218,10 +3134,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>45820</v>
       </c>
       <c r="B50" t="inlineStr">
@@ -3278,10 +3193,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>45820</v>
       </c>
       <c r="B51" t="inlineStr">
@@ -3294,7 +3208,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>Rosà</t>
@@ -3334,10 +3247,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45820</v>
       </c>
       <c r="B52" t="inlineStr">
@@ -3350,7 +3262,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>Rosà</t>
@@ -3390,10 +3301,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45821</v>
       </c>
       <c r="B53" t="inlineStr">
@@ -3406,7 +3316,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>Via Monsignor Pertile, 18/5</t>
@@ -3446,10 +3355,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45821</v>
       </c>
       <c r="B54" t="inlineStr">
@@ -3462,7 +3370,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>Campagna Lupia</t>
@@ -3502,10 +3409,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45821</v>
       </c>
       <c r="B55" t="inlineStr">
@@ -3518,7 +3424,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -3558,10 +3463,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45821</v>
       </c>
       <c r="B56" t="inlineStr">
@@ -3574,7 +3478,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
           <t>San Pietro in Gu</t>
@@ -3614,10 +3517,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45821</v>
       </c>
       <c r="B57" t="inlineStr">
@@ -3630,7 +3532,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>Adria</t>
@@ -3670,10 +3571,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45821</v>
       </c>
       <c r="B58" t="inlineStr">
@@ -3686,7 +3586,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t>Adria</t>
@@ -3726,10 +3625,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45822</v>
       </c>
       <c r="B59" t="inlineStr">
@@ -3742,7 +3640,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
           <t>Verona</t>
@@ -3782,10 +3679,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45822</v>
       </c>
       <c r="B60" t="inlineStr">
@@ -3798,7 +3694,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t xml:space="preserve">Martellago </t>
@@ -3838,10 +3733,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45822</v>
       </c>
       <c r="B61" t="inlineStr">
@@ -3854,7 +3748,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t xml:space="preserve">Martellago </t>
@@ -3894,10 +3787,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45822</v>
       </c>
       <c r="B62" t="inlineStr">
@@ -3910,7 +3802,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
           <t>Verona</t>
@@ -3950,10 +3841,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45823</v>
       </c>
       <c r="B63" t="inlineStr">
@@ -3966,7 +3856,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>Cittadella</t>
@@ -4006,10 +3895,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45823</v>
       </c>
       <c r="B64" t="inlineStr">
@@ -4022,7 +3910,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>Via Thaon di Revel 36</t>
@@ -4062,10 +3949,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45823</v>
       </c>
       <c r="B65" t="inlineStr">
@@ -4078,7 +3964,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -4118,10 +4003,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45823</v>
       </c>
       <c r="B66" t="inlineStr">
@@ -4134,7 +4018,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
           <t>Montegalda</t>
@@ -4174,10 +4057,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45823</v>
       </c>
       <c r="B67" t="inlineStr">
@@ -4190,7 +4072,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>Montegalda</t>
@@ -4230,10 +4111,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45823</v>
       </c>
       <c r="B68" t="inlineStr">
@@ -4246,7 +4126,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>Montegalda</t>
@@ -4286,10 +4165,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45823</v>
       </c>
       <c r="B69" t="inlineStr">
@@ -4302,7 +4180,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>Montegalda</t>
@@ -4342,10 +4219,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45823</v>
       </c>
       <c r="B70" t="inlineStr">
@@ -4358,7 +4234,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>Montegalda</t>
@@ -4398,10 +4273,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45823</v>
       </c>
       <c r="B71" t="inlineStr">
@@ -4414,7 +4288,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>Montegalda</t>
@@ -4454,10 +4327,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>45823</v>
       </c>
       <c r="B72" t="inlineStr">
@@ -4470,7 +4342,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>Montegalda</t>
@@ -4510,10 +4381,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>45824</v>
       </c>
       <c r="B73" t="inlineStr">
@@ -4526,7 +4396,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>Via Pazzana 1</t>
@@ -4537,7 +4406,11 @@
           <t>Mestre</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
       <c r="H73" t="n">
         <v>45.4943063</v>
       </c>
@@ -4562,10 +4435,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>45824</v>
       </c>
       <c r="B74" t="inlineStr">
@@ -4578,7 +4450,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>Arcella</t>
@@ -4618,10 +4489,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>45824</v>
       </c>
       <c r="B75" t="inlineStr">
@@ -4634,7 +4504,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>Villanova di Camposampiero</t>
@@ -4679,7 +4548,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>45824</v>
       </c>
       <c r="B76" t="inlineStr">
@@ -4692,7 +4561,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
           <t>Villanova di Camposampiero</t>
@@ -4732,10 +4600,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>45824</v>
       </c>
       <c r="B77" t="inlineStr">
@@ -4748,7 +4615,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>Via Pepe 10</t>
@@ -4759,7 +4625,6 @@
           <t>Povolaro di Dueville</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
         <v>45.6268991</v>
       </c>
@@ -4784,10 +4649,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>45824</v>
       </c>
       <c r="B78" t="inlineStr">
@@ -4800,7 +4664,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>Breganze</t>
@@ -4845,7 +4708,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>45824</v>
       </c>
       <c r="B79" t="inlineStr">
@@ -4858,7 +4721,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>Torreglia</t>
@@ -4898,10 +4760,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>45825</v>
       </c>
       <c r="B80" t="inlineStr">
@@ -4914,7 +4775,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>Altopiano di Asiago</t>
@@ -4954,10 +4814,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>45825</v>
       </c>
       <c r="B81" t="inlineStr">
@@ -4970,7 +4829,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
           <t>Via delle industrie 2/c</t>
@@ -5010,10 +4868,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>45825</v>
       </c>
       <c r="B82" t="inlineStr">
@@ -5026,7 +4883,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
           <t>Bassano del Grappa</t>
@@ -5066,10 +4922,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>45825</v>
       </c>
       <c r="B83" t="inlineStr">
@@ -5082,7 +4937,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>Cassola</t>
@@ -5122,10 +4976,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>45826</v>
       </c>
       <c r="B84" t="inlineStr">
@@ -5138,7 +4991,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>Santa Maria Di Sala</t>
@@ -5178,10 +5030,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>45826</v>
       </c>
       <c r="B85" t="inlineStr">
@@ -5194,7 +5045,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>Cinto Euganeo</t>
@@ -5234,10 +5084,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>45826</v>
       </c>
       <c r="B86" t="inlineStr">
@@ -5250,7 +5099,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t>Cinto Euganeo</t>
@@ -5290,10 +5138,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>45826</v>
       </c>
       <c r="B87" t="inlineStr">
@@ -5306,7 +5153,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
           <t>Via Zanon</t>
@@ -5346,10 +5192,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>45826</v>
       </c>
       <c r="B88" t="inlineStr">
@@ -5362,7 +5207,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>Via Zanon</t>
@@ -5402,10 +5246,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>45826</v>
       </c>
       <c r="B89" t="inlineStr">
@@ -5418,7 +5261,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -5458,10 +5300,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>45827</v>
       </c>
       <c r="B90" t="inlineStr">
@@ -5474,7 +5315,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
           <t>Via Pascoli 16</t>
@@ -5514,10 +5354,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>45827</v>
       </c>
       <c r="B91" t="inlineStr">
@@ -5530,7 +5369,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
           <t>Via Meldelssohn 2/B</t>
@@ -5570,10 +5408,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>45827</v>
       </c>
       <c r="B92" t="inlineStr">
@@ -5586,7 +5423,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
           <t>Pianiga</t>
@@ -5626,10 +5462,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>45827</v>
       </c>
       <c r="B93" t="inlineStr">
@@ -5642,7 +5477,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
           <t>Via San Lazzaro 41</t>
@@ -5682,10 +5516,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>45827</v>
       </c>
       <c r="B94" t="inlineStr">
@@ -5698,7 +5531,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
           <t>Via San Lazzaro 41</t>
@@ -5738,10 +5570,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>45827</v>
       </c>
       <c r="B95" t="inlineStr">
@@ -5754,7 +5585,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
           <t>Strada delle Cattane, 16</t>
@@ -5794,10 +5624,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>45828</v>
       </c>
       <c r="B96" t="inlineStr">
@@ -5810,7 +5639,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
           <t>Contrada Valdicase 11</t>
@@ -5821,7 +5649,6 @@
           <t>Valle di Castelgomberto</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
         <v>45.5852389</v>
       </c>
@@ -5846,10 +5673,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>45828</v>
       </c>
       <c r="B97" t="inlineStr">
@@ -5862,7 +5688,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
           <t>Longare</t>
@@ -5902,10 +5727,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>45829</v>
       </c>
       <c r="B98" t="inlineStr">
@@ -5918,7 +5742,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
           <t>San Vito di Leguzzano</t>
@@ -5958,10 +5781,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>45829</v>
       </c>
       <c r="B99" t="inlineStr">
@@ -5974,7 +5796,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
           <t>Vigonza</t>
@@ -6014,10 +5835,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>45829</v>
       </c>
       <c r="B100" t="inlineStr">
@@ -6030,7 +5850,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
           <t>Pianezze</t>
@@ -6070,10 +5889,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>45829</v>
       </c>
       <c r="B101" t="inlineStr">
@@ -6086,7 +5904,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
           <t>Arzignano</t>
@@ -6126,10 +5943,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N101" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>45830</v>
       </c>
       <c r="B102" t="inlineStr">
@@ -6142,7 +5958,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
           <t>Preganziol</t>
@@ -6182,10 +5997,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>45830</v>
       </c>
       <c r="B103" t="inlineStr">
@@ -6198,7 +6012,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
           <t>Via Santa Lucia 51</t>
@@ -6238,10 +6051,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>45830</v>
       </c>
       <c r="B104" t="inlineStr">
@@ -6254,7 +6066,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
           <t>Via Santa Lucia 51</t>
@@ -6294,10 +6105,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>45830</v>
       </c>
       <c r="B105" t="inlineStr">
@@ -6310,7 +6120,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
           <t>Via Santa Lucia 51</t>
@@ -6350,10 +6159,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N105" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>45831</v>
       </c>
       <c r="B106" t="inlineStr">
@@ -6366,7 +6174,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
           <t>Via Raccola 17</t>
@@ -6406,10 +6213,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>45831</v>
       </c>
       <c r="B107" t="inlineStr">
@@ -6422,7 +6228,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
           <t>Arzignano</t>
@@ -6462,10 +6267,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N107" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>45831</v>
       </c>
       <c r="B108" t="inlineStr">
@@ -6478,7 +6282,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
           <t xml:space="preserve">Via Forcellini 172 </t>
@@ -6518,10 +6321,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N108" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>45831</v>
       </c>
       <c r="B109" t="inlineStr">
@@ -6534,7 +6336,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
           <t>Via Vallazza 15</t>
@@ -6574,10 +6375,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N109" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>45831</v>
       </c>
       <c r="B110" t="inlineStr">
@@ -6590,7 +6390,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
           <t>Verona</t>
@@ -6630,10 +6429,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>45831</v>
       </c>
       <c r="B111" t="inlineStr">
@@ -6646,7 +6444,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
           <t>Via Porte di Sopra, 65B</t>
@@ -6686,10 +6483,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>45832</v>
       </c>
       <c r="B112" t="inlineStr">
@@ -6702,7 +6498,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
           <t>Via Montà</t>
@@ -6742,10 +6537,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N112" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>45833</v>
       </c>
       <c r="B113" t="inlineStr">
@@ -6758,7 +6552,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
           <t>Sarcedo</t>
@@ -6798,10 +6591,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N113" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>45833</v>
       </c>
       <c r="B114" t="inlineStr">
@@ -6814,7 +6606,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
           <t>Sarcedo</t>
@@ -6854,10 +6645,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>45833</v>
       </c>
       <c r="B115" t="inlineStr">
@@ -6870,7 +6660,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
           <t>Villanova di Camposampiero</t>
@@ -6910,10 +6699,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N115" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>45833</v>
       </c>
       <c r="B116" t="inlineStr">
@@ -6926,7 +6714,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
           <t>Carmignano di Brenta</t>
@@ -6966,10 +6753,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N116" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>45833</v>
       </c>
       <c r="B117" t="inlineStr">
@@ -6982,7 +6768,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -7022,10 +6807,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N117" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>45833</v>
       </c>
       <c r="B118" t="inlineStr">
@@ -7038,7 +6822,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
           <t>Via Ruspoli</t>
@@ -7078,10 +6861,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N118" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>45834</v>
       </c>
       <c r="B119" t="inlineStr">
@@ -7094,7 +6876,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
           <t>Contrada Valdicese 11</t>
@@ -7105,7 +6886,6 @@
           <t>Valle di Castelgomberto</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
         <v>45.5852389</v>
       </c>
@@ -7130,10 +6910,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N119" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>45834</v>
       </c>
       <c r="B120" t="inlineStr">
@@ -7146,7 +6925,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
           <t>Zanè</t>
@@ -7186,10 +6964,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N120" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>45834</v>
       </c>
       <c r="B121" t="inlineStr">
@@ -7202,7 +6979,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
           <t>Ponte San Nicolò</t>
@@ -7242,10 +7018,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N121" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>45834</v>
       </c>
       <c r="B122" t="inlineStr">
@@ -7258,7 +7033,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
           <t>Este</t>
@@ -7298,10 +7072,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N122" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>45834</v>
       </c>
       <c r="B123" t="inlineStr">
@@ -7314,7 +7087,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
           <t>Eraclea</t>
@@ -7354,10 +7126,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N123" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>45835</v>
       </c>
       <c r="B124" t="inlineStr">
@@ -7370,7 +7141,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
           <t>Lonigo</t>
@@ -7410,10 +7180,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N124" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>45835</v>
       </c>
       <c r="B125" t="inlineStr">
@@ -7426,7 +7195,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
           <t>Vigonza</t>
@@ -7466,10 +7234,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N125" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>45835</v>
       </c>
       <c r="B126" t="inlineStr">
@@ -7482,7 +7249,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
           <t>Ponte San Nicolò</t>
@@ -7522,10 +7288,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N126" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>45835</v>
       </c>
       <c r="B127" t="inlineStr">
@@ -7538,7 +7303,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
           <t>Preganziol</t>
@@ -7578,10 +7342,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N127" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>45836</v>
       </c>
       <c r="B128" t="inlineStr">
@@ -7594,7 +7357,6 @@
           <t>Pipistrellus nathusii</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
           <t>Cavallino-Treporti</t>
@@ -7634,10 +7396,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N128" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>45836</v>
       </c>
       <c r="B129" t="inlineStr">
@@ -7650,7 +7411,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
           <t>Dueville</t>
@@ -7690,10 +7450,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N129" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>45836</v>
       </c>
       <c r="B130" t="inlineStr">
@@ -7706,7 +7465,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
           <t>Carmignano di Brenta</t>
@@ -7746,10 +7504,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N130" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>45837</v>
       </c>
       <c r="B131" t="inlineStr">
@@ -7762,7 +7519,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
           <t>Via Tedesca 69</t>
@@ -7802,10 +7558,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N131" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>45837</v>
       </c>
       <c r="B132" t="inlineStr">
@@ -7818,7 +7573,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
           <t>Montegrotto</t>
@@ -7829,7 +7583,6 @@
           <t>Montegrotto</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
         <v>45.331491</v>
       </c>
@@ -7854,10 +7607,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N132" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>45837</v>
       </c>
       <c r="B133" t="inlineStr">
@@ -7870,7 +7622,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
           <t>Contrà Torretti 45</t>
@@ -7910,10 +7661,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N133" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B134" t="inlineStr">
@@ -7926,7 +7676,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
           <t>Sandrigo</t>
@@ -7966,10 +7715,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N134" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B135" t="inlineStr">
@@ -7982,7 +7730,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
           <t>Via Mazzini 15</t>
@@ -8022,10 +7769,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N135" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B136" t="inlineStr">
@@ -8038,7 +7784,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
           <t>Mirano</t>
@@ -8078,10 +7823,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N136" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B137" t="inlineStr">
@@ -8094,7 +7838,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
           <t>Fiesso d'Artico</t>
@@ -8134,10 +7877,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N137" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B138" t="inlineStr">
@@ -8150,7 +7892,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
           <t>Via dei Roveri 16</t>
@@ -8190,10 +7931,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N138" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B139" t="inlineStr">
@@ -8206,7 +7946,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
           <t>Recoaro Terme</t>
@@ -8246,10 +7985,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N139" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B140" t="inlineStr">
@@ -8262,7 +8000,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
           <t>Via Giambattista Vico 146</t>
@@ -8302,10 +8039,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N140" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B141" t="inlineStr">
@@ -8318,7 +8054,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
           <t>Valdagno</t>
@@ -8358,10 +8093,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N141" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B142" t="inlineStr">
@@ -8374,7 +8108,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
           <t>Brendola</t>
@@ -8414,10 +8147,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N142" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B143" t="inlineStr">
@@ -8430,7 +8162,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
           <t xml:space="preserve">Via Pertile 18 </t>
@@ -8470,10 +8201,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N143" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>45840</v>
       </c>
       <c r="B144" t="inlineStr">
@@ -8486,7 +8216,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
           <t xml:space="preserve">Via Fornace 84 </t>
@@ -8521,11 +8250,9 @@
           <t>Debilitato lasciato in una siepe</t>
         </is>
       </c>
-      <c r="M144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>45840</v>
       </c>
       <c r="B145" t="inlineStr">
@@ -8538,7 +8265,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
           <t>Recoaro Terme</t>
@@ -8578,10 +8304,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N145" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>45840</v>
       </c>
       <c r="B146" t="inlineStr">
@@ -8594,7 +8319,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
           <t>Sandrigo</t>
@@ -8634,10 +8358,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N146" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>45841</v>
       </c>
       <c r="B147" t="inlineStr">
@@ -8650,7 +8373,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
           <t>Via Donizetti 7</t>
@@ -8690,10 +8412,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N147" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>45841</v>
       </c>
       <c r="B148" t="inlineStr">
@@ -8706,7 +8427,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
           <t>Valdagno</t>
@@ -8746,10 +8466,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N148" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>45841</v>
       </c>
       <c r="B149" t="inlineStr">
@@ -8762,7 +8481,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
           <t>Rosà</t>
@@ -8802,10 +8520,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N149" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>45842</v>
       </c>
       <c r="B150" t="inlineStr">
@@ -8818,7 +8535,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
           <t>Campedello</t>
@@ -8858,10 +8574,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N150" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>45842</v>
       </c>
       <c r="B151" t="inlineStr">
@@ -8874,7 +8589,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
           <t>Vigonza</t>
@@ -8914,10 +8628,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N151" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>45842</v>
       </c>
       <c r="B152" t="inlineStr">
@@ -8930,7 +8643,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
           <t>Via Musil 18</t>
@@ -8970,10 +8682,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N152" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>45842</v>
       </c>
       <c r="B153" t="inlineStr">
@@ -8986,7 +8697,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
           <t>Arcugnano</t>
@@ -9026,10 +8736,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N153" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>45843</v>
       </c>
       <c r="B154" t="inlineStr">
@@ -9042,7 +8751,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
           <t>Bolzano Vicentino</t>
@@ -9082,10 +8790,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N154" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>45843</v>
       </c>
       <c r="B155" t="inlineStr">
@@ -9098,7 +8805,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
           <t>Lozzo Atestino</t>
@@ -9138,10 +8844,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N155" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>45844</v>
       </c>
       <c r="B156" t="inlineStr">
@@ -9154,7 +8859,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
           <t>Treviso</t>
@@ -9194,10 +8898,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N156" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>45844</v>
       </c>
       <c r="B157" t="inlineStr">
@@ -9210,7 +8913,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
           <t>Selvazzano Dentro</t>
@@ -9250,10 +8952,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N157" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>45844</v>
       </c>
       <c r="B158" t="inlineStr">
@@ -9261,8 +8962,6 @@
           <t>20:08:00</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr"/>
-      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
           <t>Thiene</t>
@@ -9302,10 +9001,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N158" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>45845</v>
       </c>
       <c r="B159" t="inlineStr">
@@ -9318,7 +9016,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
           <t>Via Vivaldi 5</t>
@@ -9358,10 +9055,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N159" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>45845</v>
       </c>
       <c r="B160" t="inlineStr">
@@ -9374,7 +9070,6 @@
           <t>Rhinolophus hipposideros</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
           <t>Valstagna</t>
@@ -9414,10 +9109,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N160" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>45846</v>
       </c>
       <c r="B161" t="inlineStr">
@@ -9474,10 +9168,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N161" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>45847</v>
       </c>
       <c r="B162" t="inlineStr">
@@ -9490,7 +9183,6 @@
           <t>Plecotus sp.</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
           <t>Bassano del grappa</t>
@@ -9530,10 +9222,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N162" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>45847</v>
       </c>
       <c r="B163" t="inlineStr">
@@ -9546,7 +9237,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
           <t>Riese Pio X</t>
@@ -9586,10 +9276,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N163" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>45848</v>
       </c>
       <c r="B164" t="inlineStr">
@@ -9602,7 +9291,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
           <t>Via Gregori 27</t>
@@ -9642,10 +9330,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N164" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>45848</v>
       </c>
       <c r="B165" t="inlineStr">
@@ -9658,7 +9345,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
           <t>Torreglia</t>
@@ -9698,10 +9384,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N165" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>45848</v>
       </c>
       <c r="B166" t="inlineStr">
@@ -9714,7 +9399,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
           <t>Mogliano Veneto</t>
@@ -9754,10 +9438,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N166" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>45848</v>
       </c>
       <c r="B167" t="inlineStr">
@@ -9770,7 +9453,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
           <t>Verona</t>
@@ -9810,10 +9492,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N167" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>45849</v>
       </c>
       <c r="B168" t="inlineStr">
@@ -9826,7 +9507,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
           <t>Sovizzo</t>
@@ -9866,10 +9546,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N168" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>45849</v>
       </c>
       <c r="B169" t="inlineStr">
@@ -9882,7 +9561,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
           <t>Barbarano Mossano</t>
@@ -9922,10 +9600,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N169" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>45849</v>
       </c>
       <c r="B170" t="inlineStr">
@@ -9938,7 +9615,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
           <t>Sandrigo</t>
@@ -9978,10 +9654,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N170" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>45849</v>
       </c>
       <c r="B171" t="inlineStr">
@@ -9994,7 +9669,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
           <t>Via Capitania 10</t>
@@ -10034,10 +9708,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N171" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>45849</v>
       </c>
       <c r="B172" t="inlineStr">
@@ -10050,7 +9723,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
           <t>San Pietro Mussolino</t>
@@ -10090,10 +9762,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N172" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>45849</v>
       </c>
       <c r="B173" t="inlineStr">
@@ -10106,7 +9777,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
           <t>Santorso</t>
@@ -10146,10 +9816,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N173" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>45849</v>
       </c>
       <c r="B174" t="inlineStr">
@@ -10162,7 +9831,6 @@
           <t>Eptesicus serotinus</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
           <t>Mestrino</t>
@@ -10202,10 +9870,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N174" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>45851</v>
       </c>
       <c r="B175" t="inlineStr">
@@ -10218,7 +9885,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
           <t>Schio</t>
@@ -10258,10 +9924,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N175" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>45851</v>
       </c>
       <c r="B176" t="inlineStr">
@@ -10274,7 +9939,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
           <t>Via Capitania 10</t>
@@ -10314,10 +9978,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N176" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>45851</v>
       </c>
       <c r="B177" t="inlineStr">
@@ -10330,7 +9993,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
           <t>Sandrigo</t>
@@ -10370,10 +10032,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N177" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>45852</v>
       </c>
       <c r="B178" t="inlineStr">
@@ -10386,7 +10047,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
           <t>Schio</t>
@@ -10426,10 +10086,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N178" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>45852</v>
       </c>
       <c r="B179" t="inlineStr">
@@ -10442,7 +10101,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
           <t>Breda di Piave</t>
@@ -10482,10 +10140,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N179" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>45852</v>
       </c>
       <c r="B180" t="inlineStr">
@@ -10498,7 +10155,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
           <t>Rovereto</t>
@@ -10538,10 +10194,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N180" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>45852</v>
       </c>
       <c r="B181" t="inlineStr">
@@ -10554,7 +10209,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
           <t>Padova</t>
@@ -10594,10 +10248,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N181" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>45853</v>
       </c>
       <c r="B182" t="inlineStr">
@@ -10610,7 +10263,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
           <t>Campo San Martino</t>
@@ -10650,10 +10302,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N182" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>45859</v>
       </c>
       <c r="B183" t="inlineStr">
@@ -10666,7 +10317,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
           <t>Schio</t>
@@ -10706,10 +10356,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N183" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>45859</v>
       </c>
       <c r="B184" t="inlineStr">
@@ -10722,7 +10371,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
           <t>Mussolente</t>
@@ -10762,10 +10410,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N184" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>45860</v>
       </c>
       <c r="B185" t="inlineStr">
@@ -10778,7 +10425,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
           <t>Marostica</t>
@@ -10818,10 +10464,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N185" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>45860</v>
       </c>
       <c r="B186" t="inlineStr">
@@ -10834,7 +10479,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
           <t>Marostica</t>
@@ -10874,10 +10518,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N186" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>45861</v>
       </c>
       <c r="B187" t="inlineStr">
@@ -10890,7 +10533,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
           <t>Chiampo</t>
@@ -10930,10 +10572,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N187" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>45861</v>
       </c>
       <c r="B188" t="inlineStr">
@@ -10946,7 +10587,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
           <t>Vittorio Veneto</t>
@@ -10986,10 +10626,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N188" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>45864</v>
       </c>
       <c r="B189" t="inlineStr">
@@ -11002,7 +10641,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr">
         <is>
           <t>San Donà di Piave</t>
@@ -11042,10 +10680,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N189" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>45866</v>
       </c>
       <c r="B190" t="inlineStr">
@@ -11058,7 +10695,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
           <t>Padova</t>
@@ -11098,10 +10734,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N190" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>45868</v>
       </c>
       <c r="B191" t="inlineStr">
@@ -11114,7 +10749,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -11154,10 +10788,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N191" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>45868</v>
       </c>
       <c r="B192" t="inlineStr">
@@ -11170,7 +10803,6 @@
           <t>Eptesicus serotinus</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr">
         <is>
           <t>Rubano</t>
@@ -11210,10 +10842,9 @@
           <t>in degenza</t>
         </is>
       </c>
-      <c r="N192" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>45872</v>
       </c>
       <c r="B193" t="inlineStr">
@@ -11226,7 +10857,6 @@
           <t>Eptesicus serotinus</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
           <t>Via Grigno 16</t>
@@ -11266,10 +10896,9 @@
           <t>in degenza</t>
         </is>
       </c>
-      <c r="N193" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="B194" t="inlineStr">
@@ -11282,7 +10911,6 @@
           <t>Hypsugo Savii</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr">
         <is>
           <t>Via Lungo Giara 30/7</t>
@@ -11293,14 +10921,12 @@
           <t>San Tomio di Malo</t>
         </is>
       </c>
-      <c r="G194" t="inlineStr"/>
       <c r="H194" t="n">
         <v>45.6392605</v>
       </c>
       <c r="I194" t="n">
         <v>11.4273472</v>
       </c>
-      <c r="J194" t="inlineStr"/>
       <c r="K194" t="n">
         <v>1</v>
       </c>
@@ -11314,10 +10940,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N194" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="B195" t="inlineStr">
@@ -11330,7 +10955,6 @@
           <t>Rhinolophus hipposideros</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
           <t>Via Borgo Masotto 8</t>
@@ -11365,11 +10989,9 @@
           <t>Colonia di oltre 300 individui in una mansarda (monitorata)</t>
         </is>
       </c>
-      <c r="M195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>45877</v>
       </c>
       <c r="B196" t="inlineStr">
@@ -11382,7 +11004,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
           <t>Corso SS. Felice e Fortunato 225</t>
@@ -11422,10 +11043,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N196" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>45880</v>
       </c>
       <c r="B197" t="inlineStr">
@@ -11438,7 +11058,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
           <t>Montemerlo</t>
@@ -11478,10 +11097,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N197" t="inlineStr"/>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>45885</v>
       </c>
       <c r="B198" t="inlineStr">
@@ -11494,7 +11112,6 @@
           <t>Eptesicus serotinus</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
           <t>Cartigliano</t>
@@ -11534,10 +11151,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N198" t="inlineStr"/>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>45886</v>
       </c>
       <c r="B199" t="inlineStr">
@@ -11550,7 +11166,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
           <t>Via Ludovico Ariosto</t>
@@ -11590,10 +11205,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N199" t="inlineStr"/>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>45892</v>
       </c>
       <c r="B200" t="inlineStr">
@@ -11606,7 +11220,6 @@
           <t>Eptesicus serotinus</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
           <t>Marostica</t>
@@ -11646,10 +11259,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N200" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>45892</v>
       </c>
       <c r="B201" t="inlineStr">
@@ -11662,7 +11274,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
           <t>Via Giorgio Dal Piaz</t>
@@ -11702,10 +11313,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N201" t="inlineStr"/>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>45893</v>
       </c>
       <c r="B202" t="inlineStr">
@@ -11718,7 +11328,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
           <t xml:space="preserve">Piazza San Lorenzo </t>
@@ -11758,10 +11367,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N202" t="inlineStr"/>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>45893</v>
       </c>
       <c r="B203" t="inlineStr">
@@ -11774,7 +11382,6 @@
           <t>Eptesicus nilssonii</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
           <t>Cornigian</t>
@@ -11814,10 +11421,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N203" t="inlineStr"/>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>45894</v>
       </c>
       <c r="B204" t="inlineStr">
@@ -11830,7 +11436,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
           <t>via Pagello 93</t>
@@ -11870,10 +11475,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N204" t="inlineStr"/>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>45896</v>
       </c>
       <c r="B205" t="inlineStr">
@@ -11886,7 +11490,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -11926,10 +11529,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N205" t="inlineStr"/>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>45899</v>
       </c>
       <c r="B206" t="inlineStr">
@@ -11942,7 +11544,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr">
         <is>
           <t>vicenza</t>
@@ -11982,10 +11583,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N206" t="inlineStr"/>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>45899</v>
       </c>
       <c r="B207" t="inlineStr">
@@ -11998,7 +11598,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr">
         <is>
           <t>Maserà di Padova</t>
@@ -12038,10 +11637,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N207" t="inlineStr"/>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="B208" t="inlineStr">
@@ -12054,7 +11652,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr">
         <is>
           <t>Viale Sant'Agostino 565</t>
@@ -12094,10 +11691,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N208" t="inlineStr"/>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="B209" t="inlineStr">
@@ -12110,7 +11706,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr">
         <is>
           <t>Via Santa Lucia 4</t>
@@ -12150,10 +11745,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N209" t="inlineStr"/>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45907</v>
       </c>
       <c r="B210" t="inlineStr">
@@ -12166,7 +11760,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr">
         <is>
           <t>Contrà San Silvestro 61</t>
@@ -12206,10 +11799,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N210" t="inlineStr"/>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45909</v>
       </c>
       <c r="B211" t="inlineStr">
@@ -12266,10 +11858,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N211" t="inlineStr"/>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45909</v>
       </c>
       <c r="B212" t="inlineStr">
@@ -12326,10 +11917,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N212" t="inlineStr"/>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45910</v>
       </c>
       <c r="B213" t="inlineStr">
@@ -12342,7 +11932,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr">
         <is>
           <t>Via Jacopo Crescini 9/4</t>
@@ -12382,10 +11971,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N213" t="inlineStr"/>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45911</v>
       </c>
       <c r="B214" t="inlineStr">
@@ -12398,7 +11986,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
       <c r="E214" t="inlineStr">
         <is>
           <t>Longare</t>
@@ -12438,10 +12025,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N214" t="inlineStr"/>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45911</v>
       </c>
       <c r="B215" t="inlineStr">
@@ -12454,7 +12040,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
       <c r="E215" t="inlineStr">
         <is>
           <t>Via dei mille 187</t>
@@ -12494,10 +12079,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N215" t="inlineStr"/>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45912</v>
       </c>
       <c r="B216" t="inlineStr">
@@ -12554,10 +12138,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N216" t="inlineStr"/>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45924</v>
       </c>
       <c r="B217" t="inlineStr">
@@ -12570,7 +12153,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr">
         <is>
           <t>Marostica</t>
@@ -12610,10 +12192,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N217" t="inlineStr"/>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="B218" t="inlineStr">
@@ -12626,7 +12207,6 @@
           <t>Myotis sp.</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr">
         <is>
           <t>Via del commercio</t>
@@ -12666,10 +12246,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N218" t="inlineStr"/>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45933</v>
       </c>
       <c r="B219" t="inlineStr">
@@ -12682,7 +12261,6 @@
           <t>Plecotus sp.</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr">
         <is>
           <t>Belluno</t>
@@ -12722,10 +12300,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N219" t="inlineStr"/>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45936</v>
       </c>
       <c r="B220" t="inlineStr">
@@ -12738,7 +12315,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -12778,10 +12354,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N220" t="inlineStr"/>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45941</v>
       </c>
       <c r="B221" t="inlineStr">
@@ -12794,7 +12369,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
       <c r="E221" t="inlineStr">
         <is>
           <t>Sossano</t>
@@ -12834,10 +12408,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N221" t="inlineStr"/>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45955</v>
       </c>
       <c r="B222" t="inlineStr">
@@ -12850,7 +12423,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr">
         <is>
           <t>Sossano</t>
@@ -12890,10 +12462,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N222" t="inlineStr"/>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45955</v>
       </c>
       <c r="B223" t="inlineStr">
@@ -12906,7 +12477,6 @@
           <t>Vespertilio Murinus</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
       <c r="E223" t="inlineStr">
         <is>
           <t>Via Monte delle rose, 62</t>
@@ -12946,10 +12516,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N223" t="inlineStr"/>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45957</v>
       </c>
       <c r="B224" t="inlineStr">
@@ -12962,7 +12531,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
       <c r="E224" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -13002,10 +12570,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N224" t="inlineStr"/>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="B225" t="inlineStr">
@@ -13018,7 +12585,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -13058,10 +12624,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N225" t="inlineStr"/>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="B226" t="inlineStr">
@@ -13074,7 +12639,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr">
         <is>
           <t>Via Siracusa</t>
@@ -13114,10 +12678,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N226" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45975</v>
       </c>
       <c r="B227" t="inlineStr">
@@ -13130,7 +12693,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr">
         <is>
           <t>Via IV novembre 29</t>
@@ -13170,10 +12732,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N227" t="inlineStr"/>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45975</v>
       </c>
       <c r="B228" t="inlineStr">
@@ -13186,7 +12747,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr">
         <is>
           <t>Via Giotto</t>
@@ -13226,10 +12786,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N228" t="inlineStr"/>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45979</v>
       </c>
       <c r="B229" t="inlineStr">
@@ -13242,7 +12801,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr">
         <is>
           <t>Eraclea</t>
@@ -13282,10 +12840,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N229" t="inlineStr"/>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B230" t="inlineStr">
@@ -13298,7 +12855,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr">
         <is>
           <t>via san marco 19</t>
@@ -13338,10 +12894,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N230" t="inlineStr"/>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45996</v>
       </c>
       <c r="B231" t="inlineStr">
@@ -13354,7 +12909,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
       <c r="E231" t="inlineStr">
         <is>
           <t>Via Cesare Battisti 9/a</t>
@@ -13394,10 +12948,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N231" t="inlineStr"/>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45999</v>
       </c>
       <c r="B232" t="inlineStr">
@@ -13410,7 +12963,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
       <c r="E232" t="inlineStr">
         <is>
           <t>Teolo</t>
@@ -13450,10 +13002,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N232" t="inlineStr"/>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>46003</v>
       </c>
       <c r="B233" t="inlineStr">
@@ -13466,7 +13017,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr">
         <is>
           <t>Costabissara</t>
@@ -13506,10 +13056,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N233" t="inlineStr"/>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>46009</v>
       </c>
       <c r="B234" t="inlineStr">
@@ -13566,10 +13115,9 @@
           <t>in degenza</t>
         </is>
       </c>
-      <c r="N234" t="inlineStr"/>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>46009</v>
       </c>
       <c r="B235" t="inlineStr">
@@ -13626,10 +13174,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N235" t="inlineStr"/>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>46019</v>
       </c>
       <c r="B236" t="inlineStr">
@@ -13642,7 +13189,6 @@
           <t>Pipistrellus Kuhlii</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr">
         <is>
           <t>Schio</t>
@@ -13682,10 +13228,9 @@
           <t>in degenza</t>
         </is>
       </c>
-      <c r="N236" t="inlineStr"/>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>46020</v>
       </c>
       <c r="B237" t="inlineStr">
@@ -13698,7 +13243,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr">
         <is>
           <t>Mogliano veneto</t>
@@ -13738,7 +13282,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N237" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/app/src/main/assets/Pipistrelli 2025.xlsx
+++ b/app/src/main/assets/Pipistrelli 2025.xlsx
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>45.5220266</v>
+        <v>45.5218</v>
       </c>
       <c r="I37" t="n">
-        <v>11.7134998</v>
+        <v>11.7132</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>45.3879511</v>
+        <v>45.3882</v>
       </c>
       <c r="I38" t="n">
-        <v>11.894839</v>
+        <v>11.8951</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>45.5574648</v>
+        <v>45.5575</v>
       </c>
       <c r="I47" t="n">
-        <v>11.5609992</v>
+        <v>11.5612</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -3139,10 +3139,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>45.5574648</v>
+        <v>45.5575</v>
       </c>
       <c r="I48" t="n">
-        <v>11.5609992</v>
+        <v>11.5612</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -3423,10 +3423,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>45.7059893</v>
+        <v>45.7061</v>
       </c>
       <c r="I53" t="n">
-        <v>11.4797197</v>
+        <v>11.4795</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -4039,10 +4039,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>45.5526037</v>
+        <v>45.5528</v>
       </c>
       <c r="I64" t="n">
-        <v>11.5210334</v>
+        <v>11.5212</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -4543,10 +4543,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>45.4943063</v>
+        <v>45.4945</v>
       </c>
       <c r="I73" t="n">
-        <v>12.2418053</v>
+        <v>12.2421</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -4769,10 +4769,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>45.6268991</v>
+        <v>45.6271</v>
       </c>
       <c r="I77" t="n">
-        <v>11.5733922</v>
+        <v>11.5735</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -4995,10 +4995,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>45.536328</v>
+        <v>45.4746</v>
       </c>
       <c r="I81" t="n">
-        <v>12.1125841</v>
+        <v>12.2275</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -5499,10 +5499,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>45.6482369</v>
+        <v>45.6483</v>
       </c>
       <c r="I90" t="n">
-        <v>11.8500628</v>
+        <v>11.8502</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -5555,10 +5555,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>45.391408</v>
+        <v>45.3916</v>
       </c>
       <c r="I91" t="n">
-        <v>11.8058487</v>
+        <v>11.8059</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -5667,10 +5667,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>45.6136525</v>
+        <v>45.5416</v>
       </c>
       <c r="I93" t="n">
-        <v>11.3387349</v>
+        <v>11.5168</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -5723,10 +5723,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>45.6133972</v>
+        <v>45.5416</v>
       </c>
       <c r="I94" t="n">
-        <v>11.3387533</v>
+        <v>11.5168</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>45.5482195</v>
+        <v>45.5484</v>
       </c>
       <c r="I95" t="n">
-        <v>11.5155888</v>
+        <v>11.5158</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -6227,10 +6227,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>45.7038592</v>
+        <v>45.6948</v>
       </c>
       <c r="I103" t="n">
-        <v>11.446109</v>
+        <v>11.4325</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>45.7038592</v>
+        <v>45.6948</v>
       </c>
       <c r="I104" t="n">
-        <v>11.446109</v>
+        <v>11.4325</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -6339,10 +6339,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>45.6950009</v>
+        <v>45.6948</v>
       </c>
       <c r="I105" t="n">
-        <v>11.4326974</v>
+        <v>11.4325</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -6395,10 +6395,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>45.3123486</v>
+        <v>45.3121</v>
       </c>
       <c r="I106" t="n">
-        <v>11.7190379</v>
+        <v>11.7192</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -6507,10 +6507,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>45.3922564</v>
+        <v>45.3925</v>
       </c>
       <c r="I108" t="n">
-        <v>11.9042333</v>
+        <v>11.9045</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -8967,10 +8967,10 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>45.4408</v>
+        <v>45.48834</v>
       </c>
       <c r="I152" t="n">
-        <v>12.3155</v>
+        <v>12.23847</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
@@ -10031,10 +10031,10 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>45.7780578</v>
+        <v>45.76569</v>
       </c>
       <c r="I171" t="n">
-        <v>12.119815</v>
+        <v>12.11589</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
@@ -10311,10 +10311,10 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>45.7780578</v>
+        <v>45.76569</v>
       </c>
       <c r="I176" t="n">
-        <v>12.119815</v>
+        <v>12.11589</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
@@ -11871,10 +11871,10 @@
         </is>
       </c>
       <c r="H204" t="n">
-        <v>45.6170674</v>
+        <v>45.60331</v>
       </c>
       <c r="I204" t="n">
-        <v>11.518656</v>
+        <v>11.51731</v>
       </c>
       <c r="J204" t="inlineStr">
         <is>
@@ -12151,10 +12151,10 @@
         </is>
       </c>
       <c r="H209" t="n">
-        <v>45.408956</v>
+        <v>45.40812</v>
       </c>
       <c r="I209" t="n">
-        <v>11.8774795</v>
+        <v>11.87532</v>
       </c>
       <c r="J209" t="inlineStr">
         <is>
@@ -13171,10 +13171,10 @@
         </is>
       </c>
       <c r="H227" t="n">
-        <v>45.5782995</v>
+        <v>45.58434</v>
       </c>
       <c r="I227" t="n">
-        <v>12.6717648</v>
+        <v>12.67756</v>
       </c>
       <c r="J227" t="inlineStr">
         <is>
@@ -13339,10 +13339,10 @@
         </is>
       </c>
       <c r="H230" t="n">
-        <v>45.4162922</v>
+        <v>45.40871</v>
       </c>
       <c r="I230" t="n">
-        <v>11.9223333</v>
+        <v>11.89934</v>
       </c>
       <c r="J230" t="inlineStr">
         <is>
@@ -13567,10 +13567,10 @@
         </is>
       </c>
       <c r="H234" t="n">
-        <v>45.41162</v>
+        <v>45.4146</v>
       </c>
       <c r="I234" t="n">
-        <v>11.91681</v>
+        <v>11.9392</v>
       </c>
       <c r="J234" t="inlineStr">
         <is>
@@ -13627,10 +13627,10 @@
         </is>
       </c>
       <c r="H235" t="n">
-        <v>45.41162</v>
+        <v>45.4146</v>
       </c>
       <c r="I235" t="n">
-        <v>11.91681</v>
+        <v>11.9392</v>
       </c>
       <c r="J235" t="inlineStr">
         <is>

--- a/app/src/main/assets/Pipistrelli 2025.xlsx
+++ b/app/src/main/assets/Pipistrelli 2025.xlsx
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>45.5852389</v>
+        <v>45.585239</v>
       </c>
       <c r="I96" t="n">
-        <v>11.4094313</v>
+        <v>11.409431</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         <v>45.130809</v>
       </c>
       <c r="I109" t="n">
-        <v>11.7894731</v>
+        <v>11.789473</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -6675,10 +6675,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>45.0849847</v>
+        <v>45.084985</v>
       </c>
       <c r="I111" t="n">
-        <v>11.5863966</v>
+        <v>11.586397</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -7123,10 +7123,10 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>45.5852389</v>
+        <v>45.585239</v>
       </c>
       <c r="I119" t="n">
-        <v>11.4094313</v>
+        <v>11.409431</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -7907,10 +7907,10 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>45.5520733</v>
+        <v>45.552073</v>
       </c>
       <c r="I133" t="n">
-        <v>11.5503627</v>
+        <v>11.550363</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -8019,10 +8019,10 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>45.7081441</v>
+        <v>45.708144</v>
       </c>
       <c r="I135" t="n">
-        <v>11.5647668</v>
+        <v>11.564767</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>45.7387649</v>
+        <v>45.738765</v>
       </c>
       <c r="I138" t="n">
-        <v>11.3948109</v>
+        <v>11.394811</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -8299,10 +8299,10 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>45.5535868</v>
+        <v>45.553587</v>
       </c>
       <c r="I140" t="n">
-        <v>11.5379822</v>
+        <v>11.537982</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -8467,10 +8467,10 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>45.7072679</v>
+        <v>45.707268</v>
       </c>
       <c r="I143" t="n">
-        <v>11.4751037</v>
+        <v>11.475104</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
@@ -8523,10 +8523,10 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>45.5792261</v>
+        <v>45.579226</v>
       </c>
       <c r="I144" t="n">
-        <v>11.4987749</v>
+        <v>11.498775</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>45.6400579</v>
+        <v>45.640058</v>
       </c>
       <c r="I147" t="n">
         <v>11.555074</v>
@@ -9355,10 +9355,10 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>45.5818027</v>
+        <v>45.581803</v>
       </c>
       <c r="I159" t="n">
-        <v>11.4894285</v>
+        <v>11.489429</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>45.500791</v>
       </c>
       <c r="I164" t="n">
-        <v>11.5335561</v>
+        <v>11.533556</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
@@ -11266,7 +11266,7 @@
         <v>45.437269</v>
       </c>
       <c r="I193" t="n">
-        <v>11.8711633</v>
+        <v>11.871163</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
@@ -11319,10 +11319,10 @@
         </is>
       </c>
       <c r="H194" t="n">
-        <v>45.6392605</v>
+        <v>45.63926</v>
       </c>
       <c r="I194" t="n">
-        <v>11.4273472</v>
+        <v>11.427347</v>
       </c>
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="n">
@@ -11371,10 +11371,10 @@
         </is>
       </c>
       <c r="H195" t="n">
-        <v>45.9878178</v>
+        <v>45.987818</v>
       </c>
       <c r="I195" t="n">
-        <v>12.3288013</v>
+        <v>12.328801</v>
       </c>
       <c r="J195" t="inlineStr">
         <is>
@@ -11423,10 +11423,10 @@
         </is>
       </c>
       <c r="H196" t="n">
-        <v>45.5443882</v>
+        <v>45.544388</v>
       </c>
       <c r="I196" t="n">
-        <v>11.5323843</v>
+        <v>11.532384</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         </is>
       </c>
       <c r="H208" t="n">
-        <v>45.5173914</v>
+        <v>45.517391</v>
       </c>
       <c r="I208" t="n">
         <v>11.511616</v>
@@ -12207,10 +12207,10 @@
         </is>
       </c>
       <c r="H210" t="n">
-        <v>45.5417595</v>
+        <v>45.541759</v>
       </c>
       <c r="I210" t="n">
-        <v>11.5485553</v>
+        <v>11.548555</v>
       </c>
       <c r="J210" t="inlineStr">
         <is>
@@ -12267,10 +12267,10 @@
         </is>
       </c>
       <c r="H211" t="n">
-        <v>45.5142442</v>
+        <v>45.514244</v>
       </c>
       <c r="I211" t="n">
-        <v>11.6754991</v>
+        <v>11.675499</v>
       </c>
       <c r="J211" t="inlineStr">
         <is>
@@ -12383,10 +12383,10 @@
         </is>
       </c>
       <c r="H213" t="n">
-        <v>45.3860703</v>
+        <v>45.38607</v>
       </c>
       <c r="I213" t="n">
-        <v>11.8953236</v>
+        <v>11.895324</v>
       </c>
       <c r="J213" t="inlineStr">
         <is>
@@ -12495,10 +12495,10 @@
         </is>
       </c>
       <c r="H215" t="n">
-        <v>45.5509697</v>
+        <v>45.55097</v>
       </c>
       <c r="I215" t="n">
-        <v>11.5276317</v>
+        <v>11.527632</v>
       </c>
       <c r="J215" t="inlineStr">
         <is>
@@ -12947,10 +12947,10 @@
         </is>
       </c>
       <c r="H223" t="n">
-        <v>45.4944293</v>
+        <v>45.494429</v>
       </c>
       <c r="I223" t="n">
-        <v>11.5490746</v>
+        <v>11.549075</v>
       </c>
       <c r="J223" t="inlineStr">
         <is>
@@ -13395,10 +13395,10 @@
         </is>
       </c>
       <c r="H231" t="n">
-        <v>45.4049836</v>
+        <v>45.404984</v>
       </c>
       <c r="I231" t="n">
-        <v>11.8828294</v>
+        <v>11.882829</v>
       </c>
       <c r="J231" t="inlineStr">
         <is>
@@ -13567,10 +13567,10 @@
         </is>
       </c>
       <c r="H234" t="n">
-        <v>45.4146</v>
+        <v>45.41375</v>
       </c>
       <c r="I234" t="n">
-        <v>11.9392</v>
+        <v>11.93122</v>
       </c>
       <c r="J234" t="inlineStr">
         <is>
@@ -13627,10 +13627,10 @@
         </is>
       </c>
       <c r="H235" t="n">
-        <v>45.4146</v>
+        <v>45.41375</v>
       </c>
       <c r="I235" t="n">
-        <v>11.9392</v>
+        <v>11.93122</v>
       </c>
       <c r="J235" t="inlineStr">
         <is>

--- a/app/src/main/assets/Pipistrelli 2025.xlsx
+++ b/app/src/main/assets/Pipistrelli 2025.xlsx
@@ -13567,10 +13567,10 @@
         </is>
       </c>
       <c r="H234" t="n">
-        <v>45.4158</v>
+        <v>45.4240962</v>
       </c>
       <c r="I234" t="n">
-        <v>11.9365</v>
+        <v>11.9428703</v>
       </c>
       <c r="J234" t="inlineStr">
         <is>
@@ -13627,10 +13627,10 @@
         </is>
       </c>
       <c r="H235" t="n">
-        <v>45.4158</v>
+        <v>45.4240962</v>
       </c>
       <c r="I235" t="n">
-        <v>11.9365</v>
+        <v>11.9428703</v>
       </c>
       <c r="J235" t="inlineStr">
         <is>

--- a/app/src/main/assets/Pipistrelli 2025.xlsx
+++ b/app/src/main/assets/Pipistrelli 2025.xlsx
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>45.5218</v>
+        <v>45.5220266</v>
       </c>
       <c r="I37" t="n">
-        <v>11.7132</v>
+        <v>11.7134998</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>45.3882</v>
+        <v>45.3879511</v>
       </c>
       <c r="I38" t="n">
-        <v>11.8951</v>
+        <v>11.894839</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>45.5575</v>
+        <v>45.5574648</v>
       </c>
       <c r="I47" t="n">
-        <v>11.5612</v>
+        <v>11.5609992</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -3139,10 +3139,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>45.5575</v>
+        <v>45.5574648</v>
       </c>
       <c r="I48" t="n">
-        <v>11.5612</v>
+        <v>11.5609992</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -3423,10 +3423,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>45.7061</v>
+        <v>45.7059893</v>
       </c>
       <c r="I53" t="n">
-        <v>11.4795</v>
+        <v>11.4797197</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -4039,10 +4039,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>45.5528</v>
+        <v>45.5526037</v>
       </c>
       <c r="I64" t="n">
-        <v>11.5212</v>
+        <v>11.5210334</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -4543,10 +4543,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>45.4945</v>
+        <v>45.4943063</v>
       </c>
       <c r="I73" t="n">
-        <v>12.2421</v>
+        <v>12.2418053</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -4769,10 +4769,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>45.6271</v>
+        <v>45.6268991</v>
       </c>
       <c r="I77" t="n">
-        <v>11.5735</v>
+        <v>11.5733922</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -4995,10 +4995,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>45.4746</v>
+        <v>45.536328</v>
       </c>
       <c r="I81" t="n">
-        <v>12.2275</v>
+        <v>12.1125841</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -5499,10 +5499,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>45.6483</v>
+        <v>45.6482369</v>
       </c>
       <c r="I90" t="n">
-        <v>11.8502</v>
+        <v>11.8500628</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -5555,10 +5555,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>45.3916</v>
+        <v>45.391408</v>
       </c>
       <c r="I91" t="n">
-        <v>11.8059</v>
+        <v>11.8058487</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -5667,10 +5667,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>45.5416</v>
+        <v>45.6136525</v>
       </c>
       <c r="I93" t="n">
-        <v>11.5168</v>
+        <v>11.3387349</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -5723,10 +5723,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>45.5416</v>
+        <v>45.6133972</v>
       </c>
       <c r="I94" t="n">
-        <v>11.5168</v>
+        <v>11.3387533</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>45.5484</v>
+        <v>45.5482195</v>
       </c>
       <c r="I95" t="n">
-        <v>11.5158</v>
+        <v>11.5155888</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>45.585239</v>
+        <v>45.5852389</v>
       </c>
       <c r="I96" t="n">
-        <v>11.409431</v>
+        <v>11.4094313</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -6227,10 +6227,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>45.6948</v>
+        <v>45.7038592</v>
       </c>
       <c r="I103" t="n">
-        <v>11.4325</v>
+        <v>11.446109</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>45.6948</v>
+        <v>45.7038592</v>
       </c>
       <c r="I104" t="n">
-        <v>11.4325</v>
+        <v>11.446109</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -6339,10 +6339,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>45.6948</v>
+        <v>45.6950009</v>
       </c>
       <c r="I105" t="n">
-        <v>11.4325</v>
+        <v>11.4326974</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -6395,10 +6395,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>45.3121</v>
+        <v>45.3123486</v>
       </c>
       <c r="I106" t="n">
-        <v>11.7192</v>
+        <v>11.7190379</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -6507,10 +6507,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>45.3925</v>
+        <v>45.3922564</v>
       </c>
       <c r="I108" t="n">
-        <v>11.9045</v>
+        <v>11.9042333</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         <v>45.130809</v>
       </c>
       <c r="I109" t="n">
-        <v>11.789473</v>
+        <v>11.7894731</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -6675,10 +6675,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>45.084985</v>
+        <v>45.0849847</v>
       </c>
       <c r="I111" t="n">
-        <v>11.586397</v>
+        <v>11.5863966</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -7123,10 +7123,10 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>45.585239</v>
+        <v>45.5852389</v>
       </c>
       <c r="I119" t="n">
-        <v>11.409431</v>
+        <v>11.4094313</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -7907,10 +7907,10 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>45.552073</v>
+        <v>45.5520733</v>
       </c>
       <c r="I133" t="n">
-        <v>11.550363</v>
+        <v>11.5503627</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -8019,10 +8019,10 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>45.708144</v>
+        <v>45.7081441</v>
       </c>
       <c r="I135" t="n">
-        <v>11.564767</v>
+        <v>11.5647668</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>45.738765</v>
+        <v>45.7387649</v>
       </c>
       <c r="I138" t="n">
-        <v>11.394811</v>
+        <v>11.3948109</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -8299,10 +8299,10 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>45.553587</v>
+        <v>45.5535868</v>
       </c>
       <c r="I140" t="n">
-        <v>11.537982</v>
+        <v>11.5379822</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -8467,10 +8467,10 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>45.707268</v>
+        <v>45.7072679</v>
       </c>
       <c r="I143" t="n">
-        <v>11.475104</v>
+        <v>11.4751037</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
@@ -8523,10 +8523,10 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>45.579226</v>
+        <v>45.5792261</v>
       </c>
       <c r="I144" t="n">
-        <v>11.498775</v>
+        <v>11.4987749</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>45.640058</v>
+        <v>45.6400579</v>
       </c>
       <c r="I147" t="n">
         <v>11.555074</v>
@@ -8967,10 +8967,10 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>45.48834</v>
+        <v>45.4408</v>
       </c>
       <c r="I152" t="n">
-        <v>12.23847</v>
+        <v>12.3155</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
@@ -9355,10 +9355,10 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>45.581803</v>
+        <v>45.5818027</v>
       </c>
       <c r="I159" t="n">
-        <v>11.489429</v>
+        <v>11.4894285</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>45.500791</v>
       </c>
       <c r="I164" t="n">
-        <v>11.533556</v>
+        <v>11.5335561</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
@@ -10031,10 +10031,10 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>45.76569</v>
+        <v>45.7780578</v>
       </c>
       <c r="I171" t="n">
-        <v>12.11589</v>
+        <v>12.119815</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
@@ -10311,10 +10311,10 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>45.76569</v>
+        <v>45.7780578</v>
       </c>
       <c r="I176" t="n">
-        <v>12.11589</v>
+        <v>12.119815</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
@@ -11266,7 +11266,7 @@
         <v>45.437269</v>
       </c>
       <c r="I193" t="n">
-        <v>11.871163</v>
+        <v>11.8711633</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
@@ -11319,10 +11319,10 @@
         </is>
       </c>
       <c r="H194" t="n">
-        <v>45.63926</v>
+        <v>45.6392605</v>
       </c>
       <c r="I194" t="n">
-        <v>11.427347</v>
+        <v>11.4273472</v>
       </c>
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="n">
@@ -11371,10 +11371,10 @@
         </is>
       </c>
       <c r="H195" t="n">
-        <v>45.987818</v>
+        <v>45.9878178</v>
       </c>
       <c r="I195" t="n">
-        <v>12.328801</v>
+        <v>12.3288013</v>
       </c>
       <c r="J195" t="inlineStr">
         <is>
@@ -11423,10 +11423,10 @@
         </is>
       </c>
       <c r="H196" t="n">
-        <v>45.544388</v>
+        <v>45.5443882</v>
       </c>
       <c r="I196" t="n">
-        <v>11.532384</v>
+        <v>11.5323843</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
@@ -11871,10 +11871,10 @@
         </is>
       </c>
       <c r="H204" t="n">
-        <v>45.60331</v>
+        <v>45.6170674</v>
       </c>
       <c r="I204" t="n">
-        <v>11.51731</v>
+        <v>11.518656</v>
       </c>
       <c r="J204" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         </is>
       </c>
       <c r="H208" t="n">
-        <v>45.517391</v>
+        <v>45.5173914</v>
       </c>
       <c r="I208" t="n">
         <v>11.511616</v>
@@ -12151,10 +12151,10 @@
         </is>
       </c>
       <c r="H209" t="n">
-        <v>45.40812</v>
+        <v>45.408956</v>
       </c>
       <c r="I209" t="n">
-        <v>11.87532</v>
+        <v>11.8774795</v>
       </c>
       <c r="J209" t="inlineStr">
         <is>
@@ -12207,10 +12207,10 @@
         </is>
       </c>
       <c r="H210" t="n">
-        <v>45.541759</v>
+        <v>45.5417595</v>
       </c>
       <c r="I210" t="n">
-        <v>11.548555</v>
+        <v>11.5485553</v>
       </c>
       <c r="J210" t="inlineStr">
         <is>
@@ -12267,10 +12267,10 @@
         </is>
       </c>
       <c r="H211" t="n">
-        <v>45.514244</v>
+        <v>45.5142442</v>
       </c>
       <c r="I211" t="n">
-        <v>11.675499</v>
+        <v>11.6754991</v>
       </c>
       <c r="J211" t="inlineStr">
         <is>
@@ -12383,10 +12383,10 @@
         </is>
       </c>
       <c r="H213" t="n">
-        <v>45.38607</v>
+        <v>45.3860703</v>
       </c>
       <c r="I213" t="n">
-        <v>11.895324</v>
+        <v>11.8953236</v>
       </c>
       <c r="J213" t="inlineStr">
         <is>
@@ -12495,10 +12495,10 @@
         </is>
       </c>
       <c r="H215" t="n">
-        <v>45.55097</v>
+        <v>45.5509697</v>
       </c>
       <c r="I215" t="n">
-        <v>11.527632</v>
+        <v>11.5276317</v>
       </c>
       <c r="J215" t="inlineStr">
         <is>
@@ -12947,10 +12947,10 @@
         </is>
       </c>
       <c r="H223" t="n">
-        <v>45.494429</v>
+        <v>45.4944293</v>
       </c>
       <c r="I223" t="n">
-        <v>11.549075</v>
+        <v>11.5490746</v>
       </c>
       <c r="J223" t="inlineStr">
         <is>
@@ -13171,10 +13171,10 @@
         </is>
       </c>
       <c r="H227" t="n">
-        <v>45.58434</v>
+        <v>45.5782995</v>
       </c>
       <c r="I227" t="n">
-        <v>12.67756</v>
+        <v>12.6717648</v>
       </c>
       <c r="J227" t="inlineStr">
         <is>
@@ -13339,10 +13339,10 @@
         </is>
       </c>
       <c r="H230" t="n">
-        <v>45.40871</v>
+        <v>45.4162922</v>
       </c>
       <c r="I230" t="n">
-        <v>11.89934</v>
+        <v>11.9223333</v>
       </c>
       <c r="J230" t="inlineStr">
         <is>
@@ -13395,10 +13395,10 @@
         </is>
       </c>
       <c r="H231" t="n">
-        <v>45.404984</v>
+        <v>45.4049836</v>
       </c>
       <c r="I231" t="n">
-        <v>11.882829</v>
+        <v>11.8828294</v>
       </c>
       <c r="J231" t="inlineStr">
         <is>
@@ -13567,10 +13567,10 @@
         </is>
       </c>
       <c r="H234" t="n">
-        <v>45.4240962</v>
+        <v>45.4288899</v>
       </c>
       <c r="I234" t="n">
-        <v>11.9428703</v>
+        <v>11.9471853</v>
       </c>
       <c r="J234" t="inlineStr">
         <is>
@@ -13627,10 +13627,10 @@
         </is>
       </c>
       <c r="H235" t="n">
-        <v>45.4240962</v>
+        <v>45.4288899</v>
       </c>
       <c r="I235" t="n">
-        <v>11.9428703</v>
+        <v>11.9471853</v>
       </c>
       <c r="J235" t="inlineStr">
         <is>
@@ -13669,12 +13669,12 @@
       <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Schio</t>
+          <t>Valli del Pasubio</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Schio</t>
+          <t>Valli del Pasubio</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -13683,10 +13683,10 @@
         </is>
       </c>
       <c r="H236" t="n">
-        <v>45.7113511</v>
+        <v>45.7441</v>
       </c>
       <c r="I236" t="n">
-        <v>11.3553593</v>
+        <v>11.2638</v>
       </c>
       <c r="J236" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>in degenza</t>
+          <t>liberato</t>
         </is>
       </c>
       <c r="N236" t="inlineStr"/>
